--- a/raw/processedSamples/20260519_r2_CMH_USDA-blood_RT-QuIC.xlsx
+++ b/raw/processedSamples/20260519_r2_CMH_USDA-blood_RT-QuIC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265A3AD5-EFA0-4242-9CD4-168AFC1EB985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF43317C-BAA1-4865-9536-960F7C01644C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD32E0E8-2A1F-46CD-B5E6-D035360384A1}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CD32E0E8-2A1F-46CD-B5E6-D035360384A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -2988,293 +2988,293 @@
         <v>10</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="4">
+      <c r="C13" s="11">
         <v>1000</v>
       </c>
-      <c r="D13" s="4">
-        <v>100</v>
-      </c>
-      <c r="E13" s="4">
-        <v>100</v>
-      </c>
-      <c r="F13" s="4">
-        <v>100</v>
-      </c>
-      <c r="G13" s="4">
-        <v>100</v>
-      </c>
-      <c r="H13" s="4">
-        <v>100</v>
-      </c>
-      <c r="I13" s="4">
-        <v>100</v>
-      </c>
-      <c r="J13" s="4">
-        <v>100</v>
-      </c>
-      <c r="K13" s="4">
-        <v>100</v>
-      </c>
-      <c r="L13" s="4">
-        <v>100</v>
-      </c>
-      <c r="M13" s="4">
-        <v>100</v>
-      </c>
-      <c r="N13" s="4">
-        <v>100</v>
-      </c>
-      <c r="O13" s="4">
+      <c r="D13" s="12">
+        <v>4</v>
+      </c>
+      <c r="E13" s="12">
+        <v>4</v>
+      </c>
+      <c r="F13" s="12">
+        <v>4</v>
+      </c>
+      <c r="G13" s="12">
+        <v>4</v>
+      </c>
+      <c r="H13" s="12">
+        <v>4</v>
+      </c>
+      <c r="I13" s="12">
+        <v>4</v>
+      </c>
+      <c r="J13" s="12">
+        <v>4</v>
+      </c>
+      <c r="K13" s="12">
+        <v>4</v>
+      </c>
+      <c r="L13" s="12">
+        <v>4</v>
+      </c>
+      <c r="M13" s="12">
+        <v>4</v>
+      </c>
+      <c r="N13" s="12">
+        <v>4</v>
+      </c>
+      <c r="O13" s="11">
         <v>1000</v>
       </c>
-      <c r="P13" s="4">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>100</v>
-      </c>
-      <c r="R13" s="4">
-        <v>100</v>
-      </c>
-      <c r="S13" s="4">
-        <v>100</v>
-      </c>
-      <c r="T13" s="4">
-        <v>100</v>
-      </c>
-      <c r="U13" s="4">
-        <v>100</v>
-      </c>
-      <c r="V13" s="4">
-        <v>100</v>
-      </c>
-      <c r="W13" s="4">
-        <v>100</v>
-      </c>
-      <c r="X13" s="4">
-        <v>100</v>
-      </c>
-      <c r="Y13" s="4">
-        <v>100</v>
-      </c>
-      <c r="Z13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AA13" s="4">
+      <c r="P13" s="12">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>4</v>
+      </c>
+      <c r="R13" s="12">
+        <v>4</v>
+      </c>
+      <c r="S13" s="12">
+        <v>4</v>
+      </c>
+      <c r="T13" s="12">
+        <v>4</v>
+      </c>
+      <c r="U13" s="12">
+        <v>4</v>
+      </c>
+      <c r="V13" s="12">
+        <v>4</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
+      <c r="X13" s="12">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA13" s="11">
         <v>1000</v>
       </c>
-      <c r="AB13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AC13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AD13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AE13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AF13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AG13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AH13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AI13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AJ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AK13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AL13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AM13" s="4">
+      <c r="AB13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AC13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AD13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AG13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AI13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AK13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AL13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AM13" s="11">
         <v>1000</v>
       </c>
-      <c r="AN13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AO13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AP13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AQ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AR13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AS13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AU13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AV13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AW13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AX13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AY13" s="4">
+      <c r="AN13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AO13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AP13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AQ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AR13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AS13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AT13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AU13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AW13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AX13" s="12">
+        <v>4</v>
+      </c>
+      <c r="AY13" s="11">
         <v>1000</v>
       </c>
-      <c r="AZ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BA13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BB13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BC13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BD13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BE13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BF13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BG13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BH13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BI13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BJ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BK13" s="4">
+      <c r="AZ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BA13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BC13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BD13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BE13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BF13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BG13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BH13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BI13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BJ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BK13" s="11">
         <v>1000</v>
       </c>
-      <c r="BL13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BM13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BN13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BO13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BP13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BQ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BR13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BS13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BT13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BU13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BV13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BW13" s="4">
+      <c r="BL13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BM13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BN13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BO13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BP13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BQ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BR13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BS13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BT13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BU13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BV13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BW13" s="11">
         <v>1000</v>
       </c>
-      <c r="BX13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BY13" s="4">
-        <v>100</v>
-      </c>
-      <c r="BZ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CA13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CB13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CC13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CD13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CE13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CF13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CG13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CH13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CI13" s="4">
+      <c r="BX13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BY13" s="12">
+        <v>4</v>
+      </c>
+      <c r="BZ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CA13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CB13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CC13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CD13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CE13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CF13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CG13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CH13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CI13" s="11">
         <v>1000</v>
       </c>
-      <c r="CJ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CK13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CL13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CM13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CN13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CO13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CP13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CQ13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CR13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CS13" s="4">
-        <v>100</v>
-      </c>
-      <c r="CT13" s="5">
-        <v>100</v>
+      <c r="CJ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CK13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CL13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CM13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CN13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CO13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CP13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CQ13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CR13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CS13" s="12">
+        <v>4</v>
+      </c>
+      <c r="CT13" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:98" ht="30" x14ac:dyDescent="0.25">
